--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_2_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_2_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,82 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
     <t>pg_tot</t>
   </si>
   <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
     <t>slack_tot</t>
   </si>
   <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
     <t>Iinj_r_tot</t>
   </si>
   <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
     <t>Ibr_from_i_tot</t>
   </si>
   <si>
-    <t>qd_tot</t>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>nn_input</t>
   </si>
   <si>
     <t>pinj_tot</t>
   </si>
   <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>nn_input</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>0.43 (1.28)</t>
-  </si>
-  <si>
-    <t>65115.03 (67239.59 &gt; 3.16%)</t>
-  </si>
-  <si>
-    <t>0.39 (1.28)</t>
-  </si>
-  <si>
-    <t>65156.75 (67239.59 &gt; 3.09%)</t>
-  </si>
-  <si>
-    <t>-0.81 (1.28)</t>
-  </si>
-  <si>
-    <t>67668.44 (67239.59 &gt; 1.37%)</t>
-  </si>
-  <si>
-    <t>-0.78 (1.28)</t>
-  </si>
-  <si>
-    <t>67295.59 (67239.59 &gt; 0.37%)</t>
+    <t>65140.88 (67239.59 &gt; 3.12%)</t>
+  </si>
+  <si>
+    <t>0.42 (128.36)</t>
+  </si>
+  <si>
+    <t>65169.12 (67239.59 &gt; 3.08%)</t>
+  </si>
+  <si>
+    <t>0.39 (128.36)</t>
+  </si>
+  <si>
+    <t>67668.43 (67239.59 &gt; 0.64%)</t>
+  </si>
+  <si>
+    <t>-0.81 (128.36)</t>
+  </si>
+  <si>
+    <t>67295.58 (67239.59 &gt; 0.08%)</t>
+  </si>
+  <si>
+    <t>-0.78 (128.36)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -489,33 +492,33 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>8.132995624602044E-05</v>
+        <v>2.949573204876745</v>
       </c>
       <c r="C2">
-        <v>0.00033321739515051</v>
+        <v>2.949526308670488</v>
       </c>
       <c r="D2">
-        <v>0.06956981867551804</v>
+        <v>0.0140627883374691</v>
       </c>
       <c r="E2">
-        <v>0.06644516438245773</v>
+        <v>0.0118864057585597</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
+      <c r="B3">
+        <v>3.159564136841265</v>
+      </c>
+      <c r="C3">
+        <v>3.159511245485554</v>
+      </c>
+      <c r="D3">
+        <v>0.01473816018551588</v>
+      </c>
+      <c r="E3">
+        <v>0.01257354207336903</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -523,33 +526,33 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.5915965437889099</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.5915982127189636</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3.429872958804481E-05</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.0003287569852545857</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>0.1260251700878143</v>
-      </c>
-      <c r="C5">
-        <v>0.1260251700878143</v>
-      </c>
-      <c r="D5">
-        <v>0.08539779484272003</v>
-      </c>
-      <c r="E5">
-        <v>0.1140894293785095</v>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,16 +560,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>10.35649237842035</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>10.35617188311696</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.04451300203800201</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.03995499759912491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -574,16 +577,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.024612474299174</v>
+        <v>0.7115272879600525</v>
       </c>
       <c r="C7">
-        <v>1.024595630237937</v>
+        <v>0.7115119695663452</v>
       </c>
       <c r="D7">
-        <v>0.03776514157652855</v>
+        <v>0.0001253670488949865</v>
       </c>
       <c r="E7">
-        <v>0.0414491780102253</v>
+        <v>0.0001645795564400032</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -608,50 +611,38 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>9.861144065856934</v>
+        <v>7.127672736090312E-05</v>
       </c>
       <c r="C9">
-        <v>9.860849380493164</v>
+        <v>0.0003312177484648146</v>
       </c>
       <c r="D9">
-        <v>0.04632531479001045</v>
+        <v>0.06957000494003296</v>
       </c>
       <c r="E9">
-        <v>0.04363924637436867</v>
+        <v>0.06644551455974579</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
-        <v>0.7115288972854614</v>
-      </c>
-      <c r="C10">
-        <v>0.7115132808685303</v>
-      </c>
-      <c r="D10">
-        <v>0.0001253659283975139</v>
-      </c>
-      <c r="E10">
-        <v>0.0001645757147343829</v>
-      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.076201270797637</v>
+        <v>0.1260304003953934</v>
       </c>
       <c r="C11">
-        <v>1.076187503864404</v>
+        <v>0.1260304003953934</v>
       </c>
       <c r="D11">
-        <v>0.03607520088553429</v>
+        <v>0.08541392534971237</v>
       </c>
       <c r="E11">
-        <v>0.03958729654550552</v>
+        <v>0.1141090244054794</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -659,33 +650,33 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.002454443601891398</v>
+        <v>1.076186750822012</v>
       </c>
       <c r="C12">
-        <v>0.0024544398766011</v>
+        <v>1.076182890290706</v>
       </c>
       <c r="D12">
-        <v>3.561158882803284E-05</v>
+        <v>0.03608011826872826</v>
       </c>
       <c r="E12">
-        <v>0.0003397512773517519</v>
+        <v>0.03959260880947113</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13">
-        <v>1.201995491981506</v>
-      </c>
-      <c r="C13">
-        <v>1.201950907707214</v>
-      </c>
-      <c r="D13">
-        <v>0.1135137751698494</v>
-      </c>
-      <c r="E13">
-        <v>0.1261488348245621</v>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -693,16 +684,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.5915994644165039</v>
+        <v>10.356405244353</v>
       </c>
       <c r="C14">
-        <v>0.5915969610214233</v>
+        <v>10.35614769855078</v>
       </c>
       <c r="D14">
-        <v>3.429925709497184E-05</v>
+        <v>0.04451272264122963</v>
       </c>
       <c r="E14">
-        <v>0.0003287592262495309</v>
+        <v>0.0399550087749958</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,33 +701,33 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>2.949590721948574</v>
+        <v>1.201976418495178</v>
       </c>
       <c r="C15">
-        <v>2.949528199374257</v>
+        <v>1.201944351196289</v>
       </c>
       <c r="D15">
-        <v>0.0140628581866622</v>
+        <v>0.1135210245847702</v>
       </c>
       <c r="E15">
-        <v>0.01188637968152761</v>
+        <v>0.1261575818061829</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>30</v>
+      <c r="B16">
+        <v>1.08680111061327</v>
+      </c>
+      <c r="C16">
+        <v>1.08677546263988</v>
+      </c>
+      <c r="D16">
+        <v>0.1127670854330063</v>
+      </c>
+      <c r="E16">
+        <v>0.1256696879863739</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -744,16 +735,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1.024609576883088</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1.024602134002988</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.03776924684643745</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.0414537712931633</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -761,16 +752,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1.086808953157098</v>
+        <v>0.002454422181472182</v>
       </c>
       <c r="C18">
-        <v>1.086781326955516</v>
+        <v>0.002454420318827033</v>
       </c>
       <c r="D18">
-        <v>0.1127597466111183</v>
+        <v>3.561102130333893E-05</v>
       </c>
       <c r="E18">
-        <v>0.1256608068943024</v>
+        <v>0.000339749181875959</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -778,16 +769,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>3.15959640407877</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>3.159526523146979</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.01473822258412838</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.01257355976849794</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>9.861069679260254</v>
+      </c>
+      <c r="C20">
+        <v>9.860823631286621</v>
+      </c>
+      <c r="D20">
+        <v>0.04632525518536568</v>
+      </c>
+      <c r="E20">
+        <v>0.04363943263888359</v>
       </c>
     </row>
   </sheetData>
